--- a/tsetmc-fund-holders.xlsx
+++ b/tsetmc-fund-holders.xlsx
@@ -41843,7 +41843,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>تسه‌مکو فقط دارندگان ≥ آستانه (معمولاً ۱٪) را منتشر می‌کند؛ پس درصد پوشش &lt; ۱۰۰ است.</t>
+          <t>tsetmc فقط دارندگان ≥ آستانه (معمولاً ۱٪) را منتشر می‌کند؛ پس درصد پوشش &lt; ۱۰۰ است.</t>
         </is>
       </c>
     </row>
@@ -41855,7 +41855,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>تغییر تعداد واحد نسبت به گزارش قبلی تسه‌مکو (مثبت/منفی) — ستون شمارش واحد حذف شده است.</t>
+          <t>تغییر تعداد واحد نسبت به گزارش قبلی tsetmc (مثبت/منفی) — ستون شمارش واحد حذف شده است.</t>
         </is>
       </c>
     </row>
